--- a/Fase 2/Evidencias Grupales/documentacion/Casos de pruebas.xlsx
+++ b/Fase 2/Evidencias Grupales/documentacion/Casos de pruebas.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Chimimserra\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\insantibanez\Music\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{8721E260-380C-452E-8118-79E9F5E3D0D8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{CBF57AAB-1FF8-4DBE-BDE8-B8363BD07414}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="1" xr2:uid="{3584A81A-8DC3-432E-A5F2-12F0D8B5A374}"/>
+    <workbookView xWindow="384" yWindow="384" windowWidth="17280" windowHeight="8880" activeTab="1" xr2:uid="{3584A81A-8DC3-432E-A5F2-12F0D8B5A374}"/>
   </bookViews>
   <sheets>
     <sheet name="Clientes" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="96" uniqueCount="53">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="96" uniqueCount="54">
   <si>
     <t>ID caso</t>
   </si>
@@ -243,6 +243,9 @@
       <t xml:space="preserve"> en su título y descripción.</t>
     </r>
   </si>
+  <si>
+    <t>ID desc</t>
+  </si>
 </sst>
 </file>
 
@@ -265,15 +268,33 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="3" tint="0.749992370372631"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -281,12 +302,30 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -622,297 +661,297 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2F9B7DE4-6093-4788-AB1F-D732CD5D1F7D}">
   <dimension ref="A1:B46"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="18.7109375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="174.5703125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="18.6640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="174.5546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A1" t="s">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="1" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A2" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A3" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A4" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A5" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A6" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A9" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B2" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
+      <c r="B9" s="1" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A10" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A11" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
+      <c r="B11" s="2" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A12" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="B4" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
+      <c r="B12" s="3" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A13" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="B5" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
+      <c r="B13" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A14" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="B6" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
+      <c r="B14" s="3" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A17" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B9" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A10" t="s">
+      <c r="B17" s="1" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A18" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="B18" s="1" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A19" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B19" s="2" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A20" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="B20" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="B21" s="3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A22" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="B22" s="3" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A25" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B10" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A11" t="s">
+      <c r="B25" s="1" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A26" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="B26" s="1" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A27" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B11" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A12" t="s">
+      <c r="B27" s="2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A28" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="B12" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A13" t="s">
+      <c r="B28" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A29" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="B13" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A14" t="s">
+      <c r="B29" s="3" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A30" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="B14" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A17" t="s">
+      <c r="B30" s="3" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="33" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A33" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B17" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A18" t="s">
+      <c r="B33" s="1" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="34" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A34" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="B34" s="1" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="35" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A35" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B35" s="2" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="36" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A36" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="B36" s="3" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="37" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A37" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="B37" s="3" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="38" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A38" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="B38" s="3" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="41" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A41" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B18" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A19" t="s">
+      <c r="B41" s="1" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="42" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A42" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="B42" s="1" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="43" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A43" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B19" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A20" t="s">
+      <c r="B43" s="2" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="44" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A44" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="B20" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A21" t="s">
+      <c r="B44" s="3" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="45" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A45" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="B21" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A22" t="s">
+      <c r="B45" s="3" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="46" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A46" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="B22" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A25" t="s">
-        <v>0</v>
-      </c>
-      <c r="B25" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A26" t="s">
-        <v>0</v>
-      </c>
-      <c r="B26" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A27" t="s">
-        <v>1</v>
-      </c>
-      <c r="B27" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A28" t="s">
-        <v>2</v>
-      </c>
-      <c r="B28" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A29" t="s">
-        <v>3</v>
-      </c>
-      <c r="B29" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A30" t="s">
-        <v>4</v>
-      </c>
-      <c r="B30" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A33" t="s">
-        <v>0</v>
-      </c>
-      <c r="B33" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A34" t="s">
-        <v>0</v>
-      </c>
-      <c r="B34" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="35" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A35" t="s">
-        <v>1</v>
-      </c>
-      <c r="B35" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="36" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A36" t="s">
-        <v>2</v>
-      </c>
-      <c r="B36" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="37" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A37" t="s">
-        <v>3</v>
-      </c>
-      <c r="B37" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="38" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A38" t="s">
-        <v>4</v>
-      </c>
-      <c r="B38" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="41" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A41" t="s">
-        <v>0</v>
-      </c>
-      <c r="B41" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="42" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A42" t="s">
-        <v>0</v>
-      </c>
-      <c r="B42" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="43" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A43" t="s">
-        <v>1</v>
-      </c>
-      <c r="B43" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="44" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A44" t="s">
-        <v>2</v>
-      </c>
-      <c r="B44" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="45" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A45" t="s">
-        <v>3</v>
-      </c>
-      <c r="B45" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="46" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A46" t="s">
-        <v>4</v>
-      </c>
-      <c r="B46" t="s">
+      <c r="B46" s="3" t="s">
         <v>40</v>
       </c>
     </row>
@@ -924,105 +963,105 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9A927091-6A99-4F43-BCAB-4BF470ED17FC}">
   <dimension ref="A1:B14"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="18.7109375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="241.85546875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="18.6640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="126" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A1" t="s">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="1" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A2" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A3" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A4" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A5" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A6" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A9" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B2" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
+      <c r="B9" s="1" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A10" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A11" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B3" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
+      <c r="B11" s="2" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A12" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="B4" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
+      <c r="B12" s="3" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A13" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="B5" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
+      <c r="B13" s="3" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A14" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="B6" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
-        <v>0</v>
-      </c>
-      <c r="B9" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A10" t="s">
-        <v>0</v>
-      </c>
-      <c r="B10" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A11" t="s">
-        <v>1</v>
-      </c>
-      <c r="B11" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A12" t="s">
-        <v>2</v>
-      </c>
-      <c r="B12" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A13" t="s">
-        <v>3</v>
-      </c>
-      <c r="B13" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A14" t="s">
-        <v>4</v>
-      </c>
-      <c r="B14" t="s">
+      <c r="B14" s="3" t="s">
         <v>52</v>
       </c>
     </row>
